--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.0253981305783962</v>
       </c>
       <c r="C2" t="n">
-        <v>43489404</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>43489404</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>30778115</v>
+        <v>3969791</v>
       </c>
       <c r="L2" t="n">
-        <v>17862849</v>
+        <v>2050152</v>
       </c>
       <c r="M2" t="n">
-        <v>4630561</v>
+        <v>481548</v>
       </c>
       <c r="N2" t="n">
-        <v>270377</v>
+        <v>21359</v>
       </c>
       <c r="O2" t="n">
-        <v>2753767</v>
+        <v>303230</v>
       </c>
       <c r="P2" t="n">
-        <v>1119861</v>
+        <v>131071</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999309182167053</v>
+        <v>0.9998471140861511</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8930894136428833</v>
+        <v>0.806284487247467</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7909663915634155</v>
+        <v>0.6354707479476929</v>
       </c>
       <c r="T2" t="n">
-        <v>0.708294689655304</v>
+        <v>0.5157405734062195</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5371806621551514</v>
+        <v>0.2988401353359222</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7736784815788269</v>
+        <v>0.5966076254844666</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8270571231842041</v>
+        <v>0.6774010062217712</v>
       </c>
       <c r="X2" t="n">
-        <v>43489404</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>43489404</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>29820171</v>
+        <v>3879625</v>
       </c>
       <c r="AG2" t="n">
-        <v>16515869</v>
+        <v>1931326</v>
       </c>
       <c r="AH2" t="n">
-        <v>4154683</v>
+        <v>444442</v>
       </c>
       <c r="AI2" t="n">
-        <v>239231</v>
+        <v>19781</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2526940</v>
+        <v>281899</v>
       </c>
       <c r="AK2" t="n">
-        <v>1050221</v>
+        <v>123153</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8627481460571289</v>
+        <v>0.7857089638710022</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.736375093460083</v>
+        <v>0.6027695536613464</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6408821940422058</v>
+        <v>0.479902982711792</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3867009580135345</v>
+        <v>0.2238226681947708</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7105374932289124</v>
+        <v>0.5548602938652039</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7763077616691589</v>
+        <v>0.6372300982475281</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.006709646399966036</v>
       </c>
       <c r="C3" t="n">
-        <v>910</v>
+        <v>330</v>
       </c>
       <c r="D3" t="n">
-        <v>30778115</v>
+        <v>3969791</v>
       </c>
       <c r="E3" t="n">
-        <v>3327196</v>
+        <v>836061</v>
       </c>
       <c r="F3" t="n">
-        <v>183642</v>
+        <v>53536</v>
       </c>
       <c r="G3" t="n">
-        <v>30936</v>
+        <v>7229</v>
       </c>
       <c r="H3" t="n">
-        <v>6861</v>
+        <v>3185</v>
       </c>
       <c r="I3" t="n">
-        <v>1179</v>
+        <v>460</v>
       </c>
       <c r="J3" t="n">
-        <v>69000391</v>
+        <v>9856678</v>
       </c>
       <c r="K3" t="n">
-        <v>74479553</v>
+        <v>10246038</v>
       </c>
       <c r="L3" t="n">
-        <v>85150381</v>
+        <v>11634591</v>
       </c>
       <c r="M3" t="n">
-        <v>104071965</v>
+        <v>14683638</v>
       </c>
       <c r="N3" t="n">
-        <v>111638960</v>
+        <v>15931320</v>
       </c>
       <c r="O3" t="n">
-        <v>108122586</v>
+        <v>15355185</v>
       </c>
       <c r="P3" t="n">
-        <v>110905098</v>
+        <v>15814473</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8965672850608826</v>
+        <v>0.8150531053543091</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7896336317062378</v>
+        <v>0.6289259195327759</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7108872532844543</v>
+        <v>0.5152406096458435</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4354661405086517</v>
+        <v>0.2400804758071899</v>
       </c>
       <c r="V3" t="n">
-        <v>0.77251797914505</v>
+        <v>0.5943495631217957</v>
       </c>
       <c r="W3" t="n">
-        <v>0.827362060546875</v>
+        <v>0.6773449778556824</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>29820171</v>
+        <v>3879625</v>
       </c>
       <c r="Z3" t="n">
-        <v>4179710</v>
+        <v>907451</v>
       </c>
       <c r="AA3" t="n">
-        <v>223857</v>
+        <v>61002</v>
       </c>
       <c r="AB3" t="n">
-        <v>92525</v>
+        <v>17272</v>
       </c>
       <c r="AC3" t="n">
-        <v>11121</v>
+        <v>4608</v>
       </c>
       <c r="AD3" t="n">
-        <v>1455</v>
+        <v>634</v>
       </c>
       <c r="AE3" t="n">
-        <v>69003396</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>73419966</v>
+        <v>10141695</v>
       </c>
       <c r="AG3" t="n">
-        <v>83958367</v>
+        <v>11537872</v>
       </c>
       <c r="AH3" t="n">
-        <v>103650950</v>
+        <v>14654126</v>
       </c>
       <c r="AI3" t="n">
-        <v>111492494</v>
+        <v>15912837</v>
       </c>
       <c r="AJ3" t="n">
-        <v>107898698</v>
+        <v>15334057</v>
       </c>
       <c r="AK3" t="n">
-        <v>110836648</v>
+        <v>15806783</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8686623573303223</v>
+        <v>0.7965407371520996</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.7300899028778076</v>
+        <v>0.5924736261367798</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6378300786018372</v>
+        <v>0.4755384027957916</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.385302722454071</v>
+        <v>0.2223433703184128</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.7088859081268311</v>
+        <v>0.5525394678115845</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7759114503860474</v>
+        <v>0.636426568031311</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.06292636329607457</v>
       </c>
       <c r="C4" t="n">
-        <v>426</v>
+        <v>151</v>
       </c>
       <c r="D4" t="n">
-        <v>3477012</v>
+        <v>893256</v>
       </c>
       <c r="E4" t="n">
-        <v>17862849</v>
+        <v>2050152</v>
       </c>
       <c r="F4" t="n">
-        <v>1117322</v>
+        <v>261785</v>
       </c>
       <c r="G4" t="n">
-        <v>43521</v>
+        <v>11443</v>
       </c>
       <c r="H4" t="n">
-        <v>108027</v>
+        <v>37900</v>
       </c>
       <c r="I4" t="n">
-        <v>12536</v>
+        <v>5080</v>
       </c>
       <c r="J4" t="n">
-        <v>3005</v>
+        <v>950</v>
       </c>
       <c r="K4" t="n">
-        <v>3684408</v>
+        <v>953770</v>
       </c>
       <c r="L4" t="n">
-        <v>4720726</v>
+        <v>1176042</v>
       </c>
       <c r="M4" t="n">
-        <v>1907058</v>
+        <v>452154</v>
       </c>
       <c r="N4" t="n">
-        <v>232949</v>
+        <v>50114</v>
       </c>
       <c r="O4" t="n">
-        <v>805550</v>
+        <v>205027</v>
       </c>
       <c r="P4" t="n">
-        <v>234170</v>
+        <v>62420</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999965488910675</v>
+        <v>0.9999235272407532</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8948249816894531</v>
+        <v>0.8106451034545898</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7902994155883789</v>
+        <v>0.6321814060211182</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7095886468887329</v>
+        <v>0.5154904723167419</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4810049831867218</v>
+        <v>0.2662569284439087</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7730977535247803</v>
+        <v>0.5954764485359192</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8272095918655396</v>
+        <v>0.6773729920387268</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>4459579</v>
+        <v>981669</v>
       </c>
       <c r="Z4" t="n">
-        <v>16515869</v>
+        <v>1931326</v>
       </c>
       <c r="AA4" t="n">
-        <v>1381998</v>
+        <v>275114</v>
       </c>
       <c r="AB4" t="n">
-        <v>90806</v>
+        <v>18418</v>
       </c>
       <c r="AC4" t="n">
-        <v>154265</v>
+        <v>46413</v>
       </c>
       <c r="AD4" t="n">
-        <v>19176</v>
+        <v>6827</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>4743995</v>
+        <v>1058113</v>
       </c>
       <c r="AG4" t="n">
-        <v>5912740</v>
+        <v>1272761</v>
       </c>
       <c r="AH4" t="n">
-        <v>2328073</v>
+        <v>481666</v>
       </c>
       <c r="AI4" t="n">
-        <v>379415</v>
+        <v>68597</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1029438</v>
+        <v>226155</v>
       </c>
       <c r="AK4" t="n">
-        <v>302620</v>
+        <v>70110</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8656951785087585</v>
+        <v>0.791087806224823</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7332190275192261</v>
+        <v>0.5975772738456726</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6393525004386902</v>
+        <v>0.4777107238769531</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3860006034374237</v>
+        <v>0.2230805605649948</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.7097107768058777</v>
+        <v>0.5536974668502808</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7761095762252808</v>
+        <v>0.6368280649185181</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>474</v>
+        <v>162</v>
       </c>
       <c r="D5" t="n">
-        <v>135292</v>
+        <v>43068</v>
       </c>
       <c r="E5" t="n">
-        <v>1187108</v>
+        <v>275007</v>
       </c>
       <c r="F5" t="n">
-        <v>4630561</v>
+        <v>481548</v>
       </c>
       <c r="G5" t="n">
-        <v>86810</v>
+        <v>17286</v>
       </c>
       <c r="H5" t="n">
-        <v>430686</v>
+        <v>103015</v>
       </c>
       <c r="I5" t="n">
-        <v>42846</v>
+        <v>14522</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3550724</v>
+        <v>900801</v>
       </c>
       <c r="L5" t="n">
-        <v>4758844</v>
+        <v>1209615</v>
       </c>
       <c r="M5" t="n">
-        <v>1883216</v>
+        <v>453060</v>
       </c>
       <c r="N5" t="n">
-        <v>350514</v>
+        <v>67607</v>
       </c>
       <c r="O5" t="n">
-        <v>810897</v>
+        <v>206958</v>
       </c>
       <c r="P5" t="n">
-        <v>233671</v>
+        <v>62436</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999732971191406</v>
+        <v>0.9999408721923828</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9356836080551147</v>
+        <v>0.8845970630645752</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9157317876815796</v>
+        <v>0.8515496253967285</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9663065075874329</v>
+        <v>0.9436719417572021</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9948133230209351</v>
+        <v>0.9926746487617493</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9856306910514832</v>
+        <v>0.9743637442588806</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9958411455154419</v>
+        <v>0.9922307133674622</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>191095</v>
+        <v>55693</v>
       </c>
       <c r="Z5" t="n">
-        <v>1457880</v>
+        <v>288452</v>
       </c>
       <c r="AA5" t="n">
-        <v>4154683</v>
+        <v>444442</v>
       </c>
       <c r="AB5" t="n">
-        <v>109952</v>
+        <v>18491</v>
       </c>
       <c r="AC5" t="n">
-        <v>540534</v>
+        <v>110393</v>
       </c>
       <c r="AD5" t="n">
-        <v>59633</v>
+        <v>17137</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>4508668</v>
+        <v>990967</v>
       </c>
       <c r="AG5" t="n">
-        <v>6105824</v>
+        <v>1328441</v>
       </c>
       <c r="AH5" t="n">
-        <v>2359094</v>
+        <v>490166</v>
       </c>
       <c r="AI5" t="n">
-        <v>381660</v>
+        <v>69185</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1037724</v>
+        <v>228289</v>
       </c>
       <c r="AK5" t="n">
-        <v>303311</v>
+        <v>70354</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9177488684654236</v>
+        <v>0.8724935054779053</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8931614756584167</v>
+        <v>0.8381370902061462</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9583336114883423</v>
+        <v>0.9395265579223633</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9932344555854797</v>
+        <v>0.9914263486862183</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9816240668296814</v>
+        <v>0.9717216491699219</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9946135878562927</v>
+        <v>0.9912594556808472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>793</v>
+        <v>213</v>
       </c>
       <c r="D6" t="n">
-        <v>67336</v>
+        <v>14499</v>
       </c>
       <c r="E6" t="n">
-        <v>83392</v>
+        <v>18930</v>
       </c>
       <c r="F6" t="n">
-        <v>126622</v>
+        <v>19251</v>
       </c>
       <c r="G6" t="n">
-        <v>270377</v>
+        <v>21359</v>
       </c>
       <c r="H6" t="n">
-        <v>63118</v>
+        <v>12323</v>
       </c>
       <c r="I6" t="n">
-        <v>9253</v>
+        <v>2391</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>83128</v>
+        <v>15475</v>
       </c>
       <c r="Z6" t="n">
-        <v>95644</v>
+        <v>19911</v>
       </c>
       <c r="AA6" t="n">
-        <v>116433</v>
+        <v>18620</v>
       </c>
       <c r="AB6" t="n">
-        <v>239231</v>
+        <v>19781</v>
       </c>
       <c r="AC6" t="n">
-        <v>75066</v>
+        <v>12539</v>
       </c>
       <c r="AD6" t="n">
-        <v>11389</v>
+        <v>2640</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>266</v>
+        <v>66</v>
       </c>
       <c r="D7" t="n">
-        <v>4512</v>
+        <v>2877</v>
       </c>
       <c r="E7" t="n">
-        <v>115084</v>
+        <v>42419</v>
       </c>
       <c r="F7" t="n">
-        <v>456917</v>
+        <v>109330</v>
       </c>
       <c r="G7" t="n">
-        <v>65762</v>
+        <v>12299</v>
       </c>
       <c r="H7" t="n">
-        <v>2753767</v>
+        <v>303230</v>
       </c>
       <c r="I7" t="n">
-        <v>168356</v>
+        <v>39967</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>9749</v>
+        <v>5163</v>
       </c>
       <c r="Z7" t="n">
-        <v>166537</v>
+        <v>51800</v>
       </c>
       <c r="AA7" t="n">
-        <v>572579</v>
+        <v>116271</v>
       </c>
       <c r="AB7" t="n">
-        <v>77892</v>
+        <v>12183</v>
       </c>
       <c r="AC7" t="n">
-        <v>2526940</v>
+        <v>281899</v>
       </c>
       <c r="AD7" t="n">
-        <v>210967</v>
+        <v>42872</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>136</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>256</v>
+        <v>70</v>
       </c>
       <c r="E8" t="n">
-        <v>7946</v>
+        <v>3625</v>
       </c>
       <c r="F8" t="n">
-        <v>22555</v>
+        <v>8252</v>
       </c>
       <c r="G8" t="n">
-        <v>5920</v>
+        <v>1857</v>
       </c>
       <c r="H8" t="n">
-        <v>196858</v>
+        <v>48604</v>
       </c>
       <c r="I8" t="n">
-        <v>1119861</v>
+        <v>131071</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>444</v>
+        <v>113</v>
       </c>
       <c r="Z8" t="n">
-        <v>12969</v>
+        <v>5147</v>
       </c>
       <c r="AA8" t="n">
-        <v>33206</v>
+        <v>10659</v>
       </c>
       <c r="AB8" t="n">
-        <v>8240</v>
+        <v>2233</v>
       </c>
       <c r="AC8" t="n">
-        <v>248452</v>
+        <v>52202</v>
       </c>
       <c r="AD8" t="n">
-        <v>1050221</v>
+        <v>123153</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
